--- a/listsize_summary.xlsx
+++ b/listsize_summary.xlsx
@@ -357,7 +357,7 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>List_Size_Group</t>
+          <t>Patient_Band</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -581,7 +581,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>&lt; 4,999</t>
+          <t>&lt;4,999</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -605,7 +605,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>&lt; 4,999</t>
+          <t>&lt;4,999</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
